--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:35:53+00:00</t>
+    <t>2026-09-09T13:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:47:18+00:00</t>
+    <t>2026-09-11T09:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/all-profiles.xlsx
+++ b/branches/master/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:58:18+00:00</t>
+    <t>2026-09-11T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
